--- a/data/trans_orig/IP31KM08_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM08_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39677</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30048</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50458</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,29%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>51851</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43075</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>60911</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>45,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45523</t>
+          <t>55755</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31979</t>
+          <t>47339</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59932</t>
+          <t>64978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>97375</t>
+          <t>95432</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81249</t>
+          <t>81176</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114293</t>
+          <t>109903</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83219</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>72438</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>92848</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>67,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>62400</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53340</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>71176</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>54,62%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91292</t>
+          <t>62843</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76883</t>
+          <t>53620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104836</t>
+          <t>71259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>153691</t>
+          <t>146062</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136773</t>
+          <t>131591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169817</t>
+          <t>160318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>118063</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>102561</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>132027</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>51,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>44,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>82570</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>68996</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>93968</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>44,37%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>50,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>120757</t>
+          <t>85888</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106058</t>
+          <t>74133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136611</t>
+          <t>97541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>203327</t>
+          <t>203951</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>182662</t>
+          <t>187832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>223010</t>
+          <t>221651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>113178</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>99214</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>128680</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>48,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>55,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>103544</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>92146</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>117118</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>55,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>62,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>126763</t>
+          <t>94705</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>110909</t>
+          <t>83052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141462</t>
+          <t>106460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>230307</t>
+          <t>207882</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210624</t>
+          <t>190182</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>250972</t>
+          <t>224001</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65470</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53139</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76984</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>56351</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33674</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71683</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>71847</t>
+          <t>54492</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57912</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85402</t>
+          <t>64651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>128198</t>
+          <t>119962</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96751</t>
+          <t>104373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151134</t>
+          <t>136014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>101052</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>89538</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>113383</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>68,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>131898</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>116566</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154575</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>70,07%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>61,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>111242</t>
+          <t>100546</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97687</t>
+          <t>90387</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125177</t>
+          <t>110568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>243141</t>
+          <t>201598</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220205</t>
+          <t>185546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>274588</t>
+          <t>217187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91055</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80615</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>102809</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>54,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>61,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>91316</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>79982</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>101877</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>55,5%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>61,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95649</t>
+          <t>90821</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84864</t>
+          <t>79739</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108029</t>
+          <t>101285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>186965</t>
+          <t>181875</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170411</t>
+          <t>164804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203778</t>
+          <t>197334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>75110</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63356</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>85550</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>38,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>73203</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>62642</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>84537</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44,5%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>38,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>81660</t>
+          <t>73158</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69280</t>
+          <t>62694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92445</t>
+          <t>84240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>154863</t>
+          <t>148269</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138050</t>
+          <t>132810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>171417</t>
+          <t>165340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>314265</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>289722</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>339438</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>282089</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>240513</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>305116</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,19%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>286956</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>305651</t>
+          <t>265036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>361634</t>
+          <t>307614</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>615865</t>
+          <t>601221</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>570122</t>
+          <t>565196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>653213</t>
+          <t>633148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>372559</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>347386</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>397102</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>50,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>371045</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>348018</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>412621</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>56,81%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>63,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>410957</t>
+          <t>331252</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>383099</t>
+          <t>310594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439082</t>
+          <t>353172</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>782002</t>
+          <t>703810</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>744654</t>
+          <t>671883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>827745</t>
+          <t>739835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
